--- a/spa_forms/003_skincare_product_layering_survey--spa_forms.xlsx
+++ b/spa_forms/003_skincare_product_layering_survey--spa_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'cleanser'}</t>
+          <t>cleanser</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Cleanser'}</t>
+          <t>Cleanser</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'moisturizer'}</t>
+          <t>moisturizer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Moisturizer'}</t>
+          <t>Moisturizer</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'primer'}</t>
+          <t>primer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Primer'}</t>
+          <t>Primer</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'moisturizer'}</t>
+          <t>moisturizer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Moisturizer'}</t>
+          <t>Moisturizer</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'mask'}</t>
+          <t>mask</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Mask'}</t>
+          <t>Mask</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'serum'}</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Serum'}</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'less_frequently'}</t>
+          <t>less_frequently</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Less frequently'}</t>
+          <t>Less frequently</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'serums'}</t>
+          <t>serums</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Serums'}</t>
+          <t>Serums</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'moisturizers'}</t>
+          <t>moisturizers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Moisturizers'}</t>
+          <t>Moisturizers</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'eye_creams'}</t>
+          <t>eye_creams</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Eye Creams'}</t>
+          <t>Eye Creams</t>
         </is>
       </c>
     </row>
